--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260810.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260810.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>202608WTX</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>聯詠科技</t>
+          <t>115/08台股期貨</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>9,852,000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>3.82%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>202608WTX</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>115/08台股期貨</t>
+          <t>聯詠科技</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>9,852,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.84%</t>
+          <t>3.79%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.33%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
@@ -704,68 +704,68 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>9,790,000</t>
+          <t>21,105,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>21,105,000</t>
+          <t>30,987,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>35,274,000</t>
+          <t>9,790,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -799,17 +799,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>3,816,646,641</t>
+          <t>35,274,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -821,22 +821,22 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>30,987,000</t>
+          <t>3,891,938,651</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
@@ -880,139 +880,139 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>34,365,000</t>
+          <t>11,165,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>11,165,000</t>
+          <t>34,365,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>4,126,000</t>
+          <t>6,485,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>9,520,000</t>
+          <t>4,126,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>2,820,000</t>
+          <t>9,520,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>6,485,000</t>
+          <t>2,820,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
@@ -1122,29 +1122,29 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>14,134,000</t>
+          <t>17,369,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
@@ -1188,161 +1188,161 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>9,574,000</t>
+          <t>2,535,985,322</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>17,369,000</t>
+          <t>9,574,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,452,825,322</t>
+          <t>14,134,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>543,000</t>
+          <t>14,120,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>5,975,000</t>
+          <t>6,546,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>6,546,000</t>
+          <t>543,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>14,120,000</t>
+          <t>5,975,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>13,785,000</t>
+          <t>16,505,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -1430,95 +1430,95 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>4,886,000</t>
+          <t>13,785,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>16,505,000</t>
+          <t>4,886,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>8,715,000</t>
+          <t>7,223,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>7,223,000</t>
+          <t>8,715,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1584,73 +1584,73 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>18,691,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>47,231,000</t>
+          <t>18,691,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>47,231,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-50,912,323</t>
+          <t>-4,487,572</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
